--- a/docs/中转站价格.xlsx
+++ b/docs/中转站价格.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\private\my_project\sub2api\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my_project\sub2api\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="23040" windowHeight="9324"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="53">
   <si>
     <t>渠道商</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF101114"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>Codex-Gpt-1</t>
     </r>
     <r>
@@ -221,6 +227,9 @@
   <si>
     <t>gpt-pro-0.02
 gpt-高智商-0.025</t>
+  </si>
+  <si>
+    <t>aicost</t>
   </si>
 </sst>
 </file>
@@ -854,7 +863,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -872,15 +881,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1202,13 +1202,13 @@
   <dimension ref="A1:G70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="12.625" customWidth="1"/>
-    <col min="2" max="2" width="23.625" customWidth="1"/>
+    <col min="1" max="1" width="12.6296296296296" customWidth="1"/>
+    <col min="2" max="2" width="23.6296296296296" customWidth="1"/>
     <col min="3" max="3" width="32.75" customWidth="1"/>
-    <col min="4" max="4" width="17.625" customWidth="1"/>
+    <col min="4" max="4" width="17.6296296296296" customWidth="1"/>
     <col min="5" max="5" width="14.5" customWidth="1"/>
-    <col min="6" max="6" width="14.125" customWidth="1"/>
-    <col min="7" max="7" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="14.1296296296296" customWidth="1"/>
+    <col min="7" max="7" width="12.6296296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:7">
@@ -1481,7 +1481,7 @@
     </row>
     <row r="20" customHeight="1" spans="1:7">
       <c r="A20" s="1"/>
-      <c r="B20" s="7"/>
+      <c r="B20" s="6"/>
       <c r="C20" t="s">
         <v>18</v>
       </c>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="21" customHeight="1" spans="1:7">
       <c r="A21" s="1"/>
-      <c r="B21" s="7"/>
+      <c r="B21" s="6"/>
       <c r="C21" t="s">
         <v>19</v>
       </c>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="22" customHeight="1" spans="1:7">
       <c r="A22" s="1"/>
-      <c r="B22" s="7"/>
+      <c r="B22" s="6"/>
       <c r="C22" t="s">
         <v>23</v>
       </c>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="23" customHeight="1" spans="1:7">
       <c r="A23" s="1"/>
-      <c r="B23" s="7"/>
+      <c r="B23" s="6"/>
       <c r="C23" t="s">
         <v>27</v>
       </c>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="24" customHeight="1" spans="1:7">
       <c r="A24" s="1"/>
-      <c r="B24" s="7"/>
+      <c r="B24" s="6"/>
       <c r="C24" t="s">
         <v>22</v>
       </c>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="29" customHeight="1" spans="1:7">
       <c r="A29" s="1"/>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C29" t="s">
@@ -1618,7 +1618,7 @@
     </row>
     <row r="30" customHeight="1" spans="1:7">
       <c r="A30" s="1"/>
-      <c r="B30" s="9"/>
+      <c r="B30" s="6"/>
       <c r="C30" t="s">
         <v>13</v>
       </c>
@@ -1631,7 +1631,7 @@
     </row>
     <row r="31" customHeight="1" spans="1:7">
       <c r="A31" s="1"/>
-      <c r="B31" s="9"/>
+      <c r="B31" s="6"/>
       <c r="C31" t="s">
         <v>15</v>
       </c>
@@ -1650,7 +1650,7 @@
       <c r="C32" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="7" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       <c r="A33" s="1"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="10"/>
+      <c r="D33" s="7"/>
     </row>
     <row r="34" customHeight="1" spans="1:7">
       <c r="A34" s="5" t="s">
@@ -1797,7 +1797,6 @@
       <c r="D43">
         <v>0.15</v>
       </c>
-      <c r="E43"/>
       <c r="G43" t="s">
         <v>20</v>
       </c>
@@ -1994,6 +1993,9 @@
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:7">
+      <c r="A61" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="C61" t="s">
         <v>17</v>
       </c>
@@ -2005,6 +2007,7 @@
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:7">
+      <c r="A62" s="1"/>
       <c r="C62" t="s">
         <v>18</v>
       </c>
@@ -2016,18 +2019,19 @@
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:7">
+      <c r="A63" s="1"/>
       <c r="C63" t="s">
         <v>19</v>
       </c>
       <c r="D63">
         <v>0.01</v>
       </c>
-      <c r="E63"/>
       <c r="G63" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:7">
+      <c r="A64" s="1"/>
       <c r="C64" t="s">
         <v>42</v>
       </c>
@@ -2038,7 +2042,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="2:5">
+    <row r="65" customHeight="1" spans="1:5">
+      <c r="A65" s="1"/>
       <c r="B65" s="1" t="s">
         <v>48</v>
       </c>
@@ -2052,7 +2057,8 @@
         <v>2.2</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="2:5">
+    <row r="66" customHeight="1" spans="1:5">
+      <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" t="s">
         <v>15</v>
@@ -2064,7 +2070,8 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="2:5">
+    <row r="67" customHeight="1" spans="1:5">
+      <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" t="s">
         <v>49</v>
@@ -2076,7 +2083,8 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="2:5">
+    <row r="68" customHeight="1" spans="1:5">
+      <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" t="s">
         <v>8</v>
@@ -2088,7 +2096,8 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="2:5">
+    <row r="69" customHeight="1" spans="1:5">
+      <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" t="s">
         <v>36</v>
@@ -2100,7 +2109,8 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="2:5">
+    <row r="70" customHeight="1" spans="1:5">
+      <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" t="s">
         <v>10</v>
@@ -2113,11 +2123,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="A2:A17"/>
     <mergeCell ref="A19:A32"/>
     <mergeCell ref="A34:A47"/>
     <mergeCell ref="A49:A59"/>
+    <mergeCell ref="A61:A70"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B8"/>
     <mergeCell ref="B9:B11"/>
@@ -2145,7 +2156,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2157,7 +2168,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/docs/中转站价格.xlsx
+++ b/docs/中转站价格.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my_project\sub2api\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\private\my_project\sub2api\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9324"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="54">
   <si>
     <t>渠道商</t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>cc-max-满血-0.12</t>
+  </si>
+  <si>
+    <t>gemini-0.2</t>
   </si>
   <si>
     <t>gpt-pro-0.02
@@ -1199,16 +1202,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="12.6296296296296" customWidth="1"/>
-    <col min="2" max="2" width="23.6296296296296" customWidth="1"/>
+    <col min="1" max="1" width="12.6333333333333" customWidth="1"/>
+    <col min="2" max="2" width="23.6333333333333" customWidth="1"/>
     <col min="3" max="3" width="32.75" customWidth="1"/>
-    <col min="4" max="4" width="17.6296296296296" customWidth="1"/>
+    <col min="4" max="4" width="17.6333333333333" customWidth="1"/>
     <col min="5" max="5" width="14.5" customWidth="1"/>
-    <col min="6" max="6" width="14.1296296296296" customWidth="1"/>
-    <col min="7" max="7" width="12.6296296296296" customWidth="1"/>
+    <col min="6" max="6" width="14.1333333333333" customWidth="1"/>
+    <col min="7" max="7" width="12.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:7">
@@ -1986,149 +1989,184 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" ht="36" customHeight="1" spans="1:7">
+    <row r="59" customHeight="1" spans="1:7">
       <c r="A59" s="1"/>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="C59" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59">
+        <v>0.15</v>
+      </c>
+      <c r="E59">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="1:7">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" t="s">
+        <v>36</v>
+      </c>
+      <c r="D60">
+        <v>0.4</v>
+      </c>
+      <c r="E60">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="61" customHeight="1" spans="1:7">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" ht="36" customHeight="1" spans="1:7">
+      <c r="A62" s="1"/>
+      <c r="B62" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C61" t="s">
+    </row>
+    <row r="64" customHeight="1" spans="1:7">
+      <c r="A64" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C64" t="s">
         <v>17</v>
       </c>
-      <c r="D61">
+      <c r="D64">
         <v>1</v>
       </c>
-      <c r="E61">
+      <c r="E64">
         <v>5</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="1:7">
-      <c r="A62" s="1"/>
-      <c r="C62" t="s">
+    <row r="65" customHeight="1" spans="1:7">
+      <c r="A65" s="1"/>
+      <c r="C65" t="s">
         <v>18</v>
       </c>
-      <c r="D62">
+      <c r="D65">
         <v>0.2</v>
       </c>
-      <c r="E62">
+      <c r="E65">
         <v>1</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="1:7">
-      <c r="A63" s="1"/>
-      <c r="C63" t="s">
+    <row r="66" customHeight="1" spans="1:7">
+      <c r="A66" s="1"/>
+      <c r="C66" t="s">
         <v>19</v>
       </c>
-      <c r="D63">
+      <c r="D66">
         <v>0.01</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G66" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="1:7">
-      <c r="A64" s="1"/>
-      <c r="C64" t="s">
+    <row r="67" customHeight="1" spans="1:7">
+      <c r="A67" s="1"/>
+      <c r="C67" t="s">
         <v>42</v>
       </c>
-      <c r="D64">
+      <c r="D67">
         <v>0.011</v>
       </c>
-      <c r="G64" t="s">
+      <c r="G67" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="1:5">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1" t="s">
+    <row r="68" customHeight="1" spans="1:7">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C68" t="s">
         <v>12</v>
       </c>
-      <c r="D65">
+      <c r="D68">
         <v>0.4</v>
       </c>
-      <c r="E65">
+      <c r="E68">
         <v>2.2</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="1:5">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" t="s">
-        <v>15</v>
-      </c>
-      <c r="D66">
-        <v>0.55</v>
-      </c>
-      <c r="E66">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="1:5">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" t="s">
-        <v>49</v>
-      </c>
-      <c r="D67">
-        <v>0.33</v>
-      </c>
-      <c r="E67">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="1:5">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68">
-        <v>0.3</v>
-      </c>
-      <c r="E68">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="1:5">
+    <row r="69" customHeight="1" spans="1:7">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D69">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="E69">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="1:5">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="1:7">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" t="s">
+        <v>49</v>
+      </c>
+      <c r="D70">
+        <v>0.33</v>
+      </c>
+      <c r="E70">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="1:7">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71">
+        <v>0.3</v>
+      </c>
+      <c r="E71">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="1:7">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" t="s">
+        <v>36</v>
+      </c>
+      <c r="D72">
+        <v>0.8</v>
+      </c>
+      <c r="E72">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="1:7">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" t="s">
         <v>10</v>
       </c>
-      <c r="D70">
+      <c r="D73">
         <v>0.8</v>
       </c>
-      <c r="E70">
+      <c r="E73">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="A2:A17"/>
     <mergeCell ref="A19:A32"/>
     <mergeCell ref="A34:A47"/>
-    <mergeCell ref="A49:A59"/>
-    <mergeCell ref="A61:A70"/>
+    <mergeCell ref="A49:A62"/>
+    <mergeCell ref="A64:A73"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B8"/>
     <mergeCell ref="B9:B11"/>
@@ -2143,8 +2181,9 @@
     <mergeCell ref="B49:B52"/>
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B65:B67"/>
+    <mergeCell ref="B59:B61"/>
     <mergeCell ref="B68:B70"/>
+    <mergeCell ref="B71:B73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2156,7 +2195,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2168,7 +2207,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
